--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069647</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069648</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,8 +1019,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,48 +920,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89069649</v>
+        <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>80461</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abramsån, Nb</t>
+          <t>Abrahamsån, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795011</v>
+        <v>794929</v>
       </c>
       <c r="R4" t="n">
-        <v>7350857</v>
+        <v>7350986</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,27 +1001,445 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Å genom barrskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136482365</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136482366</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abrahamsån, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>795062</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7350937</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136482366</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89069649</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Abramsån, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>795011</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7350857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Å genom barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Elvira Weibull</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/89069649</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136482353</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Abrahamsån, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>794903</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7350974</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>skalad senvuxen gran + barkfläkningar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136482353</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136482354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Abrahamsån, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>795081</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7350942</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>skalad senvuxen död gran och barkfläkningar på träden runtom.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136482354</t>
         </is>
       </c>
     </row>
@@ -1030,6 +1448,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43719-2025 artfynd.xlsx
+++ b/artfynd/A 43719-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136482365</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136482366</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
